--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -407,7 +407,7 @@
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="29.83203125" customWidth="1"/>
     <col min="8" max="8" width="33.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -437,7 +437,7 @@
         <v>bank_account</v>
       </c>
       <c r="I1" t="str">
-        <v>partner_company_name</v>
+        <v>partner_name</v>
       </c>
       <c r="J1" t="str">
         <v>notes</v>
@@ -469,7 +469,7 @@
         <v>Bank account (BankName-Last4)</v>
       </c>
       <c r="I2" t="str">
-        <v>Partner company name</v>
+        <v>Partner name</v>
       </c>
       <c r="J2" t="str">
         <v>Notes</v>

--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -408,7 +408,8 @@
     <col min="7" max="7" width="29.83203125" customWidth="1"/>
     <col min="8" max="8" width="33.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="27.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,6 +441,9 @@
         <v>partner_name</v>
       </c>
       <c r="J1" t="str">
+        <v>document_ref</v>
+      </c>
+      <c r="K1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -472,6 +476,9 @@
         <v>Partner name</v>
       </c>
       <c r="J2" t="str">
+        <v>Payment receipt reference</v>
+      </c>
+      <c r="K2" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -504,6 +511,9 @@
         <v>Korakuen SAC</v>
       </c>
       <c r="J3" t="str">
+        <v>PRY001-PY-001</v>
+      </c>
+      <c r="K3" t="str">
         <v/>
       </c>
     </row>
@@ -538,10 +548,13 @@
       <c r="J4" t="str">
         <v>Optional</v>
       </c>
+      <c r="K4" t="str">
+        <v>Optional</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -397,19 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <cols>
-    <col min="1" max="1" width="29.83203125" customWidth="1"/>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="29.83203125" customWidth="1"/>
-    <col min="8" max="8" width="33.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="27.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="31.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
+    <col min="9" max="9" width="40.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="40.83203125" customWidth="1"/>
+    <col min="12" max="12" width="27.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,7 +422,7 @@
         <v>direction</v>
       </c>
       <c r="C1" t="str">
-        <v>payment_type</v>
+        <v>partner_name</v>
       </c>
       <c r="D1" t="str">
         <v>payment_date</v>
@@ -435,27 +437,33 @@
         <v>exchange_rate</v>
       </c>
       <c r="H1" t="str">
+        <v>payment_type</v>
+      </c>
+      <c r="I1" t="str">
         <v>bank_account</v>
       </c>
-      <c r="I1" t="str">
-        <v>partner_name</v>
-      </c>
       <c r="J1" t="str">
+        <v>project_code</v>
+      </c>
+      <c r="K1" t="str">
+        <v>category</v>
+      </c>
+      <c r="L1" t="str">
         <v>document_ref</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Invoice document_ref to pay</v>
+        <v>Invoice document_ref (blank = direct transaction)</v>
       </c>
       <c r="B2" t="str">
         <v>Cash flow direction</v>
       </c>
       <c r="C2" t="str">
-        <v>Payment type</v>
+        <v>Partner name</v>
       </c>
       <c r="D2" t="str">
         <v>Payment date</v>
@@ -470,15 +478,21 @@
         <v>Exchange rate (PEN per USD)</v>
       </c>
       <c r="H2" t="str">
+        <v>Payment type</v>
+      </c>
+      <c r="I2" t="str">
         <v>Bank account (BankName-Last4)</v>
       </c>
-      <c r="I2" t="str">
-        <v>Partner name</v>
-      </c>
       <c r="J2" t="str">
+        <v>Project code (direct txn only)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Cost category (direct txn only)</v>
+      </c>
+      <c r="L2" t="str">
         <v>Payment receipt reference</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -490,7 +504,7 @@
         <v>outbound</v>
       </c>
       <c r="C3" t="str">
-        <v>regular</v>
+        <v>Korakuen SAC</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-20</v>
@@ -505,27 +519,33 @@
         <v>3.72</v>
       </c>
       <c r="H3" t="str">
+        <v>regular</v>
+      </c>
+      <c r="I3" t="str">
         <v>BCP-1234</v>
       </c>
-      <c r="I3" t="str">
-        <v>Korakuen SAC</v>
-      </c>
       <c r="J3" t="str">
+        <v>PRY001</v>
+      </c>
+      <c r="K3" t="str">
+        <v>materials</v>
+      </c>
+      <c r="L3" t="str">
         <v>PRY001-PY-001</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Must exist in DB</v>
+        <v>Must exist in DB if provided</v>
       </c>
       <c r="B4" t="str">
         <v>inbound, outbound</v>
       </c>
       <c r="C4" t="str">
-        <v>regular, detraccion, retencion</v>
+        <v>Must exist in DB</v>
       </c>
       <c r="D4" t="str">
         <v>YYYY-MM-DD</v>
@@ -537,24 +557,30 @@
         <v>USD, PEN</v>
       </c>
       <c r="G4" t="str">
-        <v>Required, 2.5–6.0</v>
+        <v>Auto-filled if blank, 2.5–6.0</v>
       </c>
       <c r="H4" t="str">
-        <v>Required for regular/detraccion</v>
+        <v>regular, detraccion, retencion (default: regular)</v>
       </c>
       <c r="I4" t="str">
-        <v>Must exist in DB</v>
+        <v>Required for regular/detraccion with invoice_document_ref</v>
       </c>
       <c r="J4" t="str">
+        <v>Optional, must exist in DB</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Required for outbound direct transactions</v>
+      </c>
+      <c r="L4" t="str">
         <v>Optional</v>
       </c>
-      <c r="K4" t="str">
+      <c r="M4" t="str">
         <v>Optional</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -1,58 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="10">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A7F37"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -60,18 +104,187 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,191 +609,1076 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="31.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" customWidth="1"/>
-    <col min="10" max="10" width="32.83203125" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" customWidth="1"/>
-    <col min="12" max="12" width="27.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Payments Template — Instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Handles two modes in the same file, determined by whether you fill invoice_document_ref. You can mix both modes — some rows with it filled, some blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mode 1: Payment against existing invoice  (fill invoice_document_ref)</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="8" customHeight="1"/>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>invoice_document_ref</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>e.g. PRY001-AP-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>inbound (collection) or outbound (payment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>partner_name</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>payment_date</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>&gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>USD or PEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>exchange_rate</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Auto-filled if blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>payment_type</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Defaults to regular. Also: detraccion, retencion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>bank_account</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Yes*</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Format: BankName-Last4 (e.g. BCP-1234). Not needed for retencion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>— Ignored</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>— Ignored</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>document_ref</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Payment receipt reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="12" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Mode 2: Direct transaction  (leave invoice_document_ref blank)</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Auto-creates an invoice + invoice item + payment in one shot. For informal cash purchases without a comprobante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>invoice_document_ref</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>This is what triggers direct transaction mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>outbound (cost) or inbound (revenue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>partner_name</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>payment_date</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>&gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>USD or PEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>exchange_rate</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Auto-filled if blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>payment_type</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>— Ignored</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Always regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>bank_account</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>— Ignored</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Always null</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Determines cost_type: with project = project_cost, without = sga</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Outbound: yes</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Must match project_cost or sga categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>document_ref</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Used as the auto-generated invoice title</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40.83203125" customWidth="1" min="1" max="1"/>
+    <col width="21.83203125" customWidth="1" min="2" max="2"/>
+    <col width="18.83203125" customWidth="1" min="3" max="3"/>
+    <col width="14.83203125" customWidth="1" min="4" max="4"/>
+    <col width="16.83203125" customWidth="1" min="5" max="5"/>
+    <col width="15.83203125" customWidth="1" min="6" max="6"/>
+    <col width="31.83203125" customWidth="1" min="7" max="7"/>
+    <col width="40.83203125" customWidth="1" min="8" max="8"/>
+    <col width="40.83203125" customWidth="1" min="9" max="9"/>
+    <col width="32.83203125" customWidth="1" min="10" max="10"/>
+    <col width="40.83203125" customWidth="1" min="11" max="11"/>
+    <col width="27.83203125" customWidth="1" min="12" max="12"/>
+    <col width="12.83203125" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>invoice_document_ref</v>
-      </c>
-      <c r="B1" t="str">
-        <v>direction</v>
-      </c>
-      <c r="C1" t="str">
-        <v>partner_name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>payment_date</v>
-      </c>
-      <c r="E1" t="str">
-        <v>amount</v>
-      </c>
-      <c r="F1" t="str">
-        <v>currency</v>
-      </c>
-      <c r="G1" t="str">
-        <v>exchange_rate</v>
-      </c>
-      <c r="H1" t="str">
-        <v>payment_type</v>
-      </c>
-      <c r="I1" t="str">
-        <v>bank_account</v>
-      </c>
-      <c r="J1" t="str">
-        <v>project_code</v>
-      </c>
-      <c r="K1" t="str">
-        <v>category</v>
-      </c>
-      <c r="L1" t="str">
-        <v>document_ref</v>
-      </c>
-      <c r="M1" t="str">
-        <v>notes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>invoice_document_ref</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>partner_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>payment_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>exchange_rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>payment_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bank_account</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_ref</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Invoice document_ref (blank = direct transaction)</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Cash flow direction</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Partner name</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Payment date</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Payment amount</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Currency code</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Exchange rate (PEN per USD)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Payment type</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Bank account (BankName-Last4)</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Project code (direct txn only)</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Cost category (direct txn only)</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Payment receipt reference</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Notes</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Invoice document_ref (blank = direct transaction)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cash flow direction</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Partner name</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Payment date</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Payment amount</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Currency code</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Exchange rate (PEN per USD)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Payment type</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bank account (BankName-Last4)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Project code (direct txn only)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cost category (direct txn only)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Payment receipt reference</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>PRY001-AP-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>outbound</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Korakuen SAC</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-20</v>
-      </c>
-      <c r="E3" t="str">
-        <v>5000.00</v>
-      </c>
-      <c r="F3" t="str">
-        <v>PEN</v>
-      </c>
-      <c r="G3" t="str">
-        <v>3.72</v>
-      </c>
-      <c r="H3" t="str">
-        <v>regular</v>
-      </c>
-      <c r="I3" t="str">
-        <v>BCP-1234</v>
-      </c>
-      <c r="J3" t="str">
-        <v>PRY001</v>
-      </c>
-      <c r="K3" t="str">
-        <v>materials</v>
-      </c>
-      <c r="L3" t="str">
-        <v>PRY001-PY-001</v>
-      </c>
-      <c r="M3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PRY001-AP-001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>outbound</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Korakuen SAC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5000.00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BCP-1234</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PRY001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PRY001-PY-001</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Must exist in DB if provided</v>
-      </c>
-      <c r="B4" t="str">
-        <v>inbound, outbound</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Must exist in DB</v>
-      </c>
-      <c r="D4" t="str">
-        <v>YYYY-MM-DD</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Required, &gt; 0</v>
-      </c>
-      <c r="F4" t="str">
-        <v>USD, PEN</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Auto-filled if blank, 2.5–6.0</v>
-      </c>
-      <c r="H4" t="str">
-        <v>regular, detraccion, retencion (default: regular)</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Required for regular/detraccion with invoice_document_ref</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Optional, must exist in DB</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Required for outbound direct transactions</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Optional</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Must exist in DB if provided</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>inbound, outbound</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Must exist in DB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Required, &gt; 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>USD, PEN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Auto-filled if blank, 2.5–6.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>regular, detraccion, retencion (default: regular)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Required for regular/detraccion with invoice_document_ref</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Optional, must exist in DB</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Required for outbound direct transactions</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>inbound</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA KORAKUEN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Interbank-6753</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>other_sga</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0681730</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Transf ALEX - seed value</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>outbound</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA KORAKUEN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Interbank-6753</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>other_sga</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>SPL090326-19 - bank financial charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>inbound</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA KORAKUEN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Interbank-6753</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>other_sga</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0157540</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Transf CONST - seed value from BCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>outbound</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA KORAKUEN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>7070</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Interbank-6753</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>other_sga</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0712409</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FX conversion to Interbank-6760</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>inbound</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA KORAKUEN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3.535</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Interbank-6760</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>other_sga</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0712413</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FX conversion from Interbank-6753 PEN</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -494,97 +494,97 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>payment_date</v>
+        <v>title</v>
       </c>
       <c r="B12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C12" t="str">
-        <v>Payment date</v>
+        <v>What appears on bank app. Defaults: Pago/Cobro/Detraccion/Retencion</v>
       </c>
       <c r="D12" t="str">
-        <v>YYYY-MM-DD</v>
+        <v>Free text</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>amount</v>
+        <v>payment_date</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
       </c>
       <c r="C13" t="str">
-        <v>Payment amount</v>
+        <v>Payment date</v>
       </c>
       <c r="D13" t="str">
-        <v>Number, &gt; 0</v>
+        <v>YYYY-MM-DD</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>currency</v>
+        <v>amount</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
       </c>
       <c r="C14" t="str">
-        <v>Currency code</v>
+        <v>Payment amount</v>
       </c>
       <c r="D14" t="str">
-        <v>USD, PEN</v>
+        <v>Number, &gt; 0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>exchange_rate</v>
+        <v>currency</v>
       </c>
       <c r="B15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C15" t="str">
-        <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
+        <v>Currency code</v>
       </c>
       <c r="D15" t="str">
-        <v>2.5–6.0</v>
+        <v>USD, PEN</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>payment_type</v>
+        <v>exchange_rate</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>Payment type. Defaults to regular if blank</v>
+        <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
       </c>
       <c r="D16" t="str">
-        <v>regular, detraccion, retencion</v>
+        <v>2.5–6.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>bank_account</v>
+        <v>payment_type</v>
       </c>
       <c r="B17" t="str">
-        <v>Yes, for invoice regular/detraccion payments</v>
+        <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>Bank account in BankName-Last4 format. Currency must match payment</v>
+        <v>Payment type. Defaults to regular if blank</v>
       </c>
       <c r="D17" t="str">
-        <v>Must exist in DB</v>
+        <v>regular, detraccion, retencion</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>project_code</v>
+        <v>bank_account</v>
       </c>
       <c r="B18" t="str">
-        <v>No (direct transactions only)</v>
+        <v>Yes, for invoice regular/detraccion payments</v>
       </c>
       <c r="C18" t="str">
-        <v>Project code for direct transactions</v>
+        <v>Bank account in BankName-Last4 format. Currency must match payment</v>
       </c>
       <c r="D18" t="str">
         <v>Must exist in DB</v>
@@ -592,100 +592,115 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>category</v>
+        <v>project_code</v>
       </c>
       <c r="B19" t="str">
-        <v>Yes, for outbound direct transactions</v>
+        <v>No (direct transactions only)</v>
       </c>
       <c r="C19" t="str">
-        <v>Cost category for direct transactions</v>
+        <v>Project code for direct transactions</v>
       </c>
       <c r="D19" t="str">
-        <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
+        <v>Must exist in DB</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>document_ref</v>
+        <v>category</v>
       </c>
       <c r="B20" t="str">
-        <v>No</v>
+        <v>Yes, for outbound direct transactions</v>
       </c>
       <c r="C20" t="str">
-        <v>Payment receipt reference</v>
+        <v>Cost category for direct transactions</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>notes</v>
+        <v>document_ref</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>Notes</v>
+        <v>Payment receipt reference</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Notes:</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>notes</v>
+      </c>
+      <c r="B22" t="str">
+        <v>No</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">  - If invoice_document_ref is provided: links payment to an existing invoice</v>
+        <v>Notes:</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">  - If invoice_document_ref is blank: creates a direct transaction (auto-generates invoice + payment)</v>
+        <v xml:space="preserve">  - If invoice_document_ref is provided: links payment to an existing invoice</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - If invoice_document_ref is blank: creates a direct transaction (auto-generates invoice + payment)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v xml:space="preserve">  - exchange_rate is auto-filled from the database if left blank</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
     <col min="9" max="9" width="40.83203125" customWidth="1"/>
-    <col min="10" max="10" width="38.83203125" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" customWidth="1"/>
-    <col min="12" max="12" width="27.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="40.83203125" customWidth="1"/>
+    <col min="11" max="11" width="38.83203125" customWidth="1"/>
+    <col min="12" max="12" width="40.83203125" customWidth="1"/>
+    <col min="13" max="13" width="27.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,33 +714,36 @@
         <v>partner_name</v>
       </c>
       <c r="D1" t="str">
+        <v>title</v>
+      </c>
+      <c r="E1" t="str">
         <v>payment_date</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>amount</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>currency</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>exchange_rate</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>payment_type</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>bank_account</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>project_code</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>category</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>document_ref</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -740,33 +758,36 @@
         <v>Partner name</v>
       </c>
       <c r="D2" t="str">
+        <v>What appears on bank app. Defaults: Pago/Cobro/Detraccion/Retencion</v>
+      </c>
+      <c r="E2" t="str">
         <v>Payment date</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Payment amount</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Currency code</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Payment type. Defaults to regular if blank</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>Bank account in BankName-Last4 format. Currency must match payment</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Project code for direct transactions</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Cost category for direct transactions</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>Payment receipt reference</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -781,33 +802,36 @@
         <v>Korakuen SAC</v>
       </c>
       <c r="D3" t="str">
+        <v>Pago cemento</v>
+      </c>
+      <c r="E3" t="str">
         <v>2026-03-20</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>5000.00</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>PEN</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>3.72</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>regular</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>BCP-1234</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>PRY001</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>materials</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>PRY001-PY-001</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v/>
       </c>
     </row>
@@ -822,39 +846,42 @@
         <v>Must exist in DB</v>
       </c>
       <c r="D4" t="str">
+        <v>Free text</v>
+      </c>
+      <c r="E4" t="str">
         <v>YYYY-MM-DD</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Number, &gt; 0</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>USD, PEN</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>2.5–6.0</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>regular, detraccion, retencion</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Must exist in DB</v>
       </c>
       <c r="J4" t="str">
         <v>Must exist in DB</v>
       </c>
       <c r="K4" t="str">
+        <v>Must exist in DB</v>
+      </c>
+      <c r="L4" t="str">
         <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -578,27 +578,27 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>bank_account</v>
+        <v>operation_number</v>
       </c>
       <c r="B18" t="str">
-        <v>Yes, for invoice regular/detraccion payments</v>
+        <v>Yes, except retencion</v>
       </c>
       <c r="C18" t="str">
-        <v>Bank account in BankName-Last4 format. Currency must match payment</v>
+        <v>Bank operation/transaction number (numero de operacion)</v>
       </c>
       <c r="D18" t="str">
-        <v>Must exist in DB</v>
+        <v>Free text</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>project_code</v>
+        <v>bank_account</v>
       </c>
       <c r="B19" t="str">
-        <v>No (direct transactions only)</v>
+        <v>Yes, for invoice regular/detraccion payments</v>
       </c>
       <c r="C19" t="str">
-        <v>Project code for direct transactions</v>
+        <v>Bank account in BankName-Last4 format. Currency must match payment</v>
       </c>
       <c r="D19" t="str">
         <v>Must exist in DB</v>
@@ -606,86 +606,100 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>category</v>
+        <v>project_code</v>
       </c>
       <c r="B20" t="str">
-        <v>Yes, for outbound direct transactions</v>
+        <v>No (direct transactions only)</v>
       </c>
       <c r="C20" t="str">
-        <v>Cost category for direct transactions</v>
+        <v>Project code for direct transactions</v>
       </c>
       <c r="D20" t="str">
-        <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
+        <v>Must exist in DB</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>document_ref</v>
+        <v>category</v>
       </c>
       <c r="B21" t="str">
-        <v>No</v>
+        <v>Yes, for outbound direct transactions</v>
       </c>
       <c r="C21" t="str">
-        <v>Payment receipt reference</v>
+        <v>Cost category for direct transactions</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>notes</v>
+        <v>document_ref</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Notes</v>
+        <v>Payment receipt reference</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Notes:</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>notes</v>
+      </c>
+      <c r="B23" t="str">
+        <v>No</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">  - If invoice_document_ref is provided: links payment to an existing invoice</v>
+        <v>Notes:</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  - If invoice_document_ref is blank: creates a direct transaction (auto-generates invoice + payment)</v>
+        <v xml:space="preserve">  - If invoice_document_ref is provided: links payment to an existing invoice</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - If invoice_document_ref is blank: creates a direct transaction (auto-generates invoice + payment)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v xml:space="preserve">  - exchange_rate is auto-filled from the database if left blank</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -697,10 +711,11 @@
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
     <col min="9" max="9" width="40.83203125" customWidth="1"/>
     <col min="10" max="10" width="40.83203125" customWidth="1"/>
-    <col min="11" max="11" width="38.83203125" customWidth="1"/>
-    <col min="12" max="12" width="40.83203125" customWidth="1"/>
-    <col min="13" max="13" width="27.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="40.83203125" customWidth="1"/>
+    <col min="12" max="12" width="38.83203125" customWidth="1"/>
+    <col min="13" max="13" width="40.83203125" customWidth="1"/>
+    <col min="14" max="14" width="27.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -732,18 +747,21 @@
         <v>payment_type</v>
       </c>
       <c r="J1" t="str">
+        <v>operation_number</v>
+      </c>
+      <c r="K1" t="str">
         <v>bank_account</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>project_code</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>category</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>document_ref</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -776,18 +794,21 @@
         <v>Payment type. Defaults to regular if blank</v>
       </c>
       <c r="J2" t="str">
+        <v>Bank operation/transaction number (numero de operacion)</v>
+      </c>
+      <c r="K2" t="str">
         <v>Bank account in BankName-Last4 format. Currency must match payment</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Project code for direct transactions</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>Cost category for direct transactions</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>Payment receipt reference</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -820,18 +841,21 @@
         <v>regular</v>
       </c>
       <c r="J3" t="str">
+        <v>00123456</v>
+      </c>
+      <c r="K3" t="str">
         <v>BCP-1234</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>PRY001</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>materials</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>PRY001-PY-001</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v/>
       </c>
     </row>
@@ -864,24 +888,27 @@
         <v>regular, detraccion, retencion</v>
       </c>
       <c r="J4" t="str">
-        <v>Must exist in DB</v>
+        <v>Free text</v>
       </c>
       <c r="K4" t="str">
         <v>Must exist in DB</v>
       </c>
       <c r="L4" t="str">
+        <v>Must exist in DB</v>
+      </c>
+      <c r="M4" t="str">
         <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
       </c>
       <c r="N4" t="str">
         <v/>
       </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/website/public/templates/payments-template.xlsx
+++ b/website/public/templates/payments-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -606,100 +606,114 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>project_code</v>
+        <v>entity_document_number</v>
       </c>
       <c r="B20" t="str">
         <v>No (direct transactions only)</v>
       </c>
       <c r="C20" t="str">
-        <v>Project code for direct transactions</v>
+        <v>Supplier/client RUC/DNI for direct transactions</v>
       </c>
       <c r="D20" t="str">
-        <v>Must exist in DB</v>
+        <v>Must exist in DB if provided</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>category</v>
+        <v>project_code</v>
       </c>
       <c r="B21" t="str">
-        <v>Yes, for outbound direct transactions</v>
+        <v>No (direct transactions only)</v>
       </c>
       <c r="C21" t="str">
-        <v>Cost category for direct transactions</v>
+        <v>Project code for direct transactions</v>
       </c>
       <c r="D21" t="str">
-        <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
+        <v>Must exist in DB</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>document_ref</v>
+        <v>category</v>
       </c>
       <c r="B22" t="str">
-        <v>No</v>
+        <v>Yes, for outbound direct transactions</v>
       </c>
       <c r="C22" t="str">
-        <v>Payment receipt reference</v>
+        <v>Cost category for direct transactions</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>notes</v>
+        <v>document_ref</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Notes</v>
+        <v>Payment receipt reference</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Notes:</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>notes</v>
+      </c>
+      <c r="B24" t="str">
+        <v>No</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  - If invoice_document_ref is provided: links payment to an existing invoice</v>
+        <v>Notes:</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  - If invoice_document_ref is blank: creates a direct transaction (auto-generates invoice + payment)</v>
+        <v xml:space="preserve">  - If invoice_document_ref is provided: links payment to an existing invoice</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - If invoice_document_ref is blank: creates a direct transaction (auto-generates invoice + payment)</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
         <v xml:space="preserve">  - exchange_rate is auto-filled from the database if left blank</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -712,10 +726,11 @@
     <col min="9" max="9" width="40.83203125" customWidth="1"/>
     <col min="10" max="10" width="40.83203125" customWidth="1"/>
     <col min="11" max="11" width="40.83203125" customWidth="1"/>
-    <col min="12" max="12" width="38.83203125" customWidth="1"/>
-    <col min="13" max="13" width="40.83203125" customWidth="1"/>
-    <col min="14" max="14" width="27.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="40.83203125" customWidth="1"/>
+    <col min="13" max="13" width="38.83203125" customWidth="1"/>
+    <col min="14" max="14" width="40.83203125" customWidth="1"/>
+    <col min="15" max="15" width="27.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,15 +768,18 @@
         <v>bank_account</v>
       </c>
       <c r="L1" t="str">
+        <v>entity_document_number</v>
+      </c>
+      <c r="M1" t="str">
         <v>project_code</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>category</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>document_ref</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -800,15 +818,18 @@
         <v>Bank account in BankName-Last4 format. Currency must match payment</v>
       </c>
       <c r="L2" t="str">
+        <v>Supplier/client RUC/DNI for direct transactions</v>
+      </c>
+      <c r="M2" t="str">
         <v>Project code for direct transactions</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>Cost category for direct transactions</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>Payment receipt reference</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -847,15 +868,18 @@
         <v>BCP-1234</v>
       </c>
       <c r="L3" t="str">
+        <v>20123456789</v>
+      </c>
+      <c r="M3" t="str">
         <v>PRY001</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>materials</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>PRY001-PY-001</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v/>
       </c>
     </row>
@@ -894,21 +918,24 @@
         <v>Must exist in DB</v>
       </c>
       <c r="L4" t="str">
+        <v>Must exist in DB if provided</v>
+      </c>
+      <c r="M4" t="str">
         <v>Must exist in DB</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>Must match cost_type (project_cost if project_code given, sga otherwise)</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
       </c>
       <c r="O4" t="str">
         <v/>
       </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>